--- a/Extracted_data_analysis/polar/Output-Transformed_data/geographical_distribution_summary.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/geographical_distribution_summary.xlsx
@@ -385,7 +385,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -576,7 +576,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B4">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -4133,7 +4133,7 @@
         <v>20054</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6158,7 +6158,7 @@
         <v>25055</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -10523,7 +10523,7 @@
         <v>20018</v>
       </c>
       <c r="K219">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -11190,10 +11190,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2">
-        <v>89.7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -11206,7 +11206,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4">
@@ -11219,7 +11219,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>

--- a/Extracted_data_analysis/polar/Output-Transformed_data/geographical_distribution_summary.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/geographical_distribution_summary.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -590,7 +590,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C2">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -630,22 +630,9 @@
         </is>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
         <v>3</v>
       </c>
     </row>
